--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-02-2026.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£15.4</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£23.66</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£38.74</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2806,36 +2806,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 299.186
-  (Session info: chrome=144.0.7559.110)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a7c9a535
-	0x7ff6a7c9a590
-	0x7ff6a7a410bd
-	0x7ff6a7a2dda9
-	0x7ff6a7a2da91
-	0x7ff6a7a2b6a7
-	0x7ff6a7a2bfff
-	0x7ff6a7a3b45a
-	0x7ff6a7a52387
-	0x7ff6a7a59a8a
-	0x7ff6a7a2c7c1
-	0x7ff6a7a520b4
-	0x7ff6a7aea26f
-	0x7ff6a7a8cc9c
-	0x7ff6a7a8dbe3
-	0x7ff6a7f77b60
-	0x7ff6a7f71f5d
-	0x7ff6a7f9311a
-	0x7ff6a7cb60a5
-	0x7ff6a7cbe73c
-	0x7ff6a7ca3844
-	0x7ff6a7ca39f6
-	0x7ff6a7c89a07
-	0x7ffb4103e8d7
-	0x7ffb41ccc53c
-</t>
+          <t>£51.65</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
